--- a/AI_AuditLog_CaoThiDiepMinh.xlsx
+++ b/AI_AuditLog_CaoThiDiepMinh.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_Uni\Sem5\SWP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6CD73F-EF86-41FA-BCFB-D01D4B96F70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7835183-1237-4CB4-A8D8-2F075E6E0308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI Audit Log" sheetId="1" r:id="rId1"/>
+    <sheet name="week 2" sheetId="2" r:id="rId2"/>
+    <sheet name="week 3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
   <si>
     <t>STT</t>
   </si>
@@ -88,13 +90,481 @@
 • Contextualization: Trong thực tế spa, Owner thường không trực tiếp quản lý booking mà chỉ xem báo cáo. AI không biết điều này nên gán quá nhiều chức năng cho Owner.
 • Creative Synthesis: Tôi bổ sung điều kiện ưu tiên khoảng cách gần khách hàng và thời gian trống gần nhất thay vì chỉ random branch. Tôi quyết định feature này là business logic trọng tâm của project.
 • Decision Ownership: Giữ 4 actor chính (Owner, Branch Manager, Staff, Customer), loại bỏ Guest vì scope SWP391 không yêu cầu tính năng cho người dùng chưa đăng ký.</t>
+  </si>
+  <si>
+    <t>Entry #</t>
+  </si>
+  <si>
+    <t>Prompt Type</t>
+  </si>
+  <si>
+    <t>Stage/Component</t>
+  </si>
+  <si>
+    <t>Problem/Context</t>
+  </si>
+  <si>
+    <t>AI Response (Summary)</t>
+  </si>
+  <si>
+    <t>Decomposition</t>
+  </si>
+  <si>
+    <t>Cần phân chia module cho hệ thống Aura Spa để dễ maintain và phân công task trong nhóm.</t>
+  </si>
+  <si>
+    <t>“Suggest a suitable module structure for a Java-based spa booking management system.”</t>
+  </si>
+  <si>
+    <t>AI đề xuất chia hệ thống thành Booking, Customer, Service và Staff Management. AI cũng gợi ý tách business logic và data layer riêng.</t>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI chia module khá hợp lý nhưng thiếu Payment và Feedback Module. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Contextualization:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Aura Spa có chức năng voucher và đánh giá dịch vụ nên cần module riêng. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Creative Synthesis:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi bổ sung Payment và Feedback Module thay vì gộp vào Booking. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Decision Ownership:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Chọn kiến trúc module riêng biệt giúp team dễ phân chia công việc và maintain hơn.</t>
+    </r>
+  </si>
+  <si>
+    <t>Pattern Recognition</t>
+  </si>
+  <si>
+    <t>Hệ thống bị trùng lịch booking khi nhiều khách đặt cùng thời điểm.</t>
+  </si>
+  <si>
+    <t>“How can I prevent duplicate bookings in a Java console application?”</t>
+  </si>
+  <si>
+    <t>AI đề xuất kiểm tra slot availability trước khi tạo booking và dùng synchronized method để tránh race condition.</t>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> synchronized chỉ phù hợp với hệ thống nhỏ và không tối ưu nếu scale lớn. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Contextualization:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Project SWP391 chỉ là local console application nên synchronized vẫn phù hợp. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Creative Synthesis:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi kết hợp validate duplicate booking theo customer + service + time slot. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Decision Ownership:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Chọn giải pháp đơn giản nhưng ổn định để phù hợp phạm vi project và deadline.</t>
+    </r>
+  </si>
+  <si>
+    <t>Algorithms / Abstraction</t>
+  </si>
+  <si>
+    <t>Cần thiết kế logic suggest chi nhánh gần nhất khi branch hiện tại đã full slot booking.</t>
+  </si>
+  <si>
+    <t>“Suggest an algorithm to recommend the nearest spa branch when the current branch has no available booking slots.”</t>
+  </si>
+  <si>
+    <t>AI đề xuất sử dụng khoảng cách địa lý kết hợp ranking branch theo available slot và độ ưu tiên khách hàng.</t>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI đúng về ranking nhưng chưa xử lý trường hợp branch gần nhất vẫn full slot. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Contextualization:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Khách hàng spa thường ưu tiên thời gian phù hợp hơn khoảng cách tuyệt đối. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Creative Synthesis:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi kết hợp khoảng cách + available slot + nearest available time để tối ưu trải nghiệm booking. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Decision Ownership:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Chọn hybrid ranking algorithm vì phù hợp business logic của Aura Spa hơn cách sort đơn giản.</t>
+    </r>
+  </si>
+  <si>
+    <t>VERIFICATION</t>
+  </si>
+  <si>
+    <t>Research Stage</t>
+  </si>
+  <si>
+    <t>Cần kiểm tra nên dùng ArrayList hay HashMap để quản lý booking data.</t>
+  </si>
+  <si>
+    <t>“Is HashMap always better than ArrayList for booking management in Java?”</t>
+  </si>
+  <si>
+    <t>AI trả lời HashMap luôn nhanh hơn vì lookup O(1) nên phù hợp hơn cho booking system.</t>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI bị oversimplification vì HashMap không phù hợp khi cần hiển thị booking theo timeline. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Contextualization:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Aura Spa cần hiển thị booking theo thời gian cho staff quản lý lịch làm việc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Creative Synthesis:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi sử dụng ArrayList cho display timeline và HashMap cho tìm kiếm nhanh theo booking ID. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Decision Ownership:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi quyết định kết hợp cả hai cấu trúc dữ liệu để cân bằng hiệu năng và usability.</t>
+    </r>
+  </si>
+  <si>
+    <t>Problem-Solving</t>
+  </si>
+  <si>
+    <t>Kiểm tra tính phù hợp của LocalDateTime cho hệ thống booking spa nhiều chi nhánh.</t>
+  </si>
+  <si>
+    <t>“In a Java booking system, should I use LocalDateTime or ZonedDateTime for handling bookings?”</t>
+  </si>
+  <si>
+    <t>AI khuyến nghị sử dụng ZonedDateTime và lưu toàn bộ booking theo UTC để hỗ trợ timezone.</t>
+  </si>
+  <si>
+    <r>
+      <t>Critical Thinking:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI đưa giải pháp quá phức tạp so với phạm vi thực tế của project. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Contextualization:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Aura Spa chỉ hoạt động tại Việt Nam nên không cần xử lý nhiều múi giờ khác nhau. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Creative Synthesis:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi sử dụng LocalDateTime để giảm complexity và dễ maintain code hơn. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Decision Ownership:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi chọn LocalDateTime vì phù hợp với context thực tế và giúp code đơn giản hơn cho SWP391.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,6 +586,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -159,7 +637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -172,6 +650,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -559,4 +1046,170 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB62A7BF-B7C2-4563-827E-2E9786AC0EEE}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.5546875" customWidth="1"/>
+    <col min="2" max="2" width="36.5546875" customWidth="1"/>
+    <col min="3" max="3" width="44.5546875" customWidth="1"/>
+    <col min="4" max="4" width="41.109375" customWidth="1"/>
+    <col min="5" max="5" width="58.77734375" customWidth="1"/>
+    <col min="6" max="6" width="60.5546875" customWidth="1"/>
+    <col min="7" max="7" width="51.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="97.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="121.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="241.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C8968A-AD0F-4486-89F5-CEA1704E51FD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>